--- a/data/input/integrantes.xlsx
+++ b/data/input/integrantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josuegiraldos/Documents/Python/worship_scheduler/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABDA71F-D2DA-3148-96E2-1D68B68332D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3A6261-B219-0C41-BFB7-54B2BAC9A477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17240" xr2:uid="{FC600FDE-6114-954A-8E10-4EF6E02B7496}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Lideres</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Marla Parada</t>
+  </si>
+  <si>
+    <t>Josue Giraldo</t>
   </si>
 </sst>
 </file>
@@ -601,6 +604,9 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
